--- a/build/temp/pages/observations-summary.xlsx
+++ b/build/temp/pages/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="70">
   <si>
     <t>Profile</t>
   </si>
@@ -170,7 +170,7 @@
     <t>CIBMTR Observation Laboratory Results: Priority Variables</t>
   </si>
   <si>
-    <t>http://fhir.nmdp.org/ig/cibmtr-reporting/ValueSet/cibmtr-priority-variables-2022 (extensible)</t>
+    <t>https://vsac.nlm.nih.gov/valueset/2.16.840.1.113762.1.4.1295.7/expansion (extensible)</t>
   </si>
   <si>
     <t>dateTimeĵ, Periodĵ, Timingĵ, instantĵ</t>
@@ -191,16 +191,19 @@
     <t>cibmtr-vital-signs</t>
   </si>
   <si>
-    <t>CIBMTR Vital Signs Results Profile (us-core)</t>
+    <t>CIBMTR Vital Signs Results Profile (US Core)</t>
   </si>
   <si>
     <t>Observation Category Codes#vital-signs</t>
   </si>
   <si>
-    <t>http://fhir.nmdp.org/ig/cibmtr-reporting/ValueSet/vital-signs (extensible)</t>
+    <t>https://vsac.nlm.nih.gov/valueset/2.16.840.1.113762.1.4.1295.1/expansion (extensible)</t>
   </si>
   <si>
     <t>dateTimeĵ, Periodĵ</t>
+  </si>
+  <si>
+    <t>Quantityĵ</t>
   </si>
   <si>
     <t>cibmtr-vital-signs-height</t>
@@ -1498,7 +1501,7 @@
         <v>62</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>18</v>
@@ -1512,10 +1515,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C34" t="s" s="2">
         <v>60</v>
@@ -1524,7 +1527,7 @@
         <v>14</v>
       </c>
       <c r="E34" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F34" t="s" s="2">
         <v>14</v>
@@ -1547,10 +1550,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C35" t="s" s="2">
         <v>60</v>
@@ -1559,7 +1562,7 @@
         <v>14</v>
       </c>
       <c r="E35" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F35" t="s" s="2">
         <v>14</v>

--- a/build/temp/pages/observations-summary.xlsx
+++ b/build/temp/pages/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="70">
   <si>
     <t>Profile</t>
   </si>
@@ -191,16 +191,19 @@
     <t>cibmtr-vital-signs</t>
   </si>
   <si>
-    <t>CIBMTR Vital Signs Results Profile (us-core)</t>
+    <t>CIBMTR Vital Signs Results Profile (US Core)</t>
   </si>
   <si>
     <t>Observation Category Codes#vital-signs</t>
   </si>
   <si>
-    <t>http://fhir.nmdp.org/ig/cibmtr-reporting/ValueSet/vital-signs (extensible)</t>
+    <t>https://vsac.nlm.nih.gov/valueset/2.16.840.1.113762.1.4.1295.1/expansion (extensible)</t>
   </si>
   <si>
     <t>dateTimeĵ, Periodĵ</t>
+  </si>
+  <si>
+    <t>Quantityĵ</t>
   </si>
   <si>
     <t>cibmtr-vital-signs-height</t>
@@ -1498,7 +1501,7 @@
         <v>62</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>18</v>
@@ -1512,10 +1515,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C34" t="s" s="2">
         <v>60</v>
@@ -1524,7 +1527,7 @@
         <v>14</v>
       </c>
       <c r="E34" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F34" t="s" s="2">
         <v>14</v>
@@ -1547,10 +1550,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C35" t="s" s="2">
         <v>60</v>
@@ -1559,7 +1562,7 @@
         <v>14</v>
       </c>
       <c r="E35" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F35" t="s" s="2">
         <v>14</v>

--- a/build/temp/pages/observations-summary.xlsx
+++ b/build/temp/pages/observations-summary.xlsx
@@ -170,7 +170,7 @@
     <t>CIBMTR Observation Laboratory Results: Priority Variables</t>
   </si>
   <si>
-    <t>https://vsac.nlm.nih.gov/valueset/2.16.840.1.113762.1.4.1295.7/expansion (extensible)</t>
+    <t>http://fhir.nmdp.org/ig/cibmtr-reporting/ValueSet/cibmtr-priority-variables-2022 (extensible)</t>
   </si>
   <si>
     <t>dateTimeĵ, Periodĵ, Timingĵ, instantĵ</t>
